--- a/foundry/resources/demo_pack/华宸物业_2026年08月_公式体检样本.xlsx
+++ b/foundry/resources/demo_pack/华宸物业_2026年08月_公式体检样本.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度收入" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径备注" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上年同期对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径备注" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
   </externalReferences>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -665,124 +666,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>上年同期（外部链接）</t>
-        </is>
-      </c>
-      <c r="B6" t="e">
-        <f>'[2025年报.xlsx]利润表'!B6</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C6" t="e">
-        <f>'[2025年报.xlsx]利润表'!C6</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D6" t="e">
-        <f>'[2025年报.xlsx]利润表'!D6</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E6" t="e">
-        <f>'[2025年报.xlsx]利润表'!E6</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F6" t="e">
-        <f>'[2025年报.xlsx]利润表'!F6</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G6" t="e">
-        <f>'[2025年报.xlsx]利润表'!G6</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H6" t="e">
-        <f>'[2025年报.xlsx]利润表'!H6</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I6" t="e">
-        <f>'[2025年报.xlsx]利润表'!I6</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J6" t="e">
-        <f>'[2025年报.xlsx]利润表'!J6</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K6" t="e">
-        <f>'[2025年报.xlsx]利润表'!K6</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L6" t="e">
-        <f>'[2025年报.xlsx]利润表'!L6</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M6" t="e">
-        <f>'[2025年报.xlsx]利润表'!M6</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N6" t="e">
+          <t>上年同期（手工录入）</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>42660</v>
+      </c>
+      <c r="C6" t="n">
+        <v>40824</v>
+      </c>
+      <c r="D6" t="n">
+        <v>43308</v>
+      </c>
+      <c r="E6" t="n">
+        <v>43848</v>
+      </c>
+      <c r="F6" t="n">
+        <v>44496</v>
+      </c>
+      <c r="G6" t="n">
+        <v>45144</v>
+      </c>
+      <c r="H6" t="n">
+        <v>44928</v>
+      </c>
+      <c r="I6" t="n">
+        <v>44787.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>45252</v>
+      </c>
+      <c r="K6" t="n">
+        <v>45684</v>
+      </c>
+      <c r="L6" t="n">
+        <v>47304</v>
+      </c>
+      <c r="M6" t="n">
+        <v>51840</v>
+      </c>
+      <c r="N6">
         <f>SUM(B6:M6)</f>
-        <v>#REF!</v>
+        <v>540075.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>预算差异</t>
+          <t>编制日期</t>
         </is>
       </c>
       <c r="B7">
-        <f>B5-B7</f>
-        <v>43845</v>
-      </c>
-      <c r="C7">
-        <f>C5-C7</f>
-        <v>41958</v>
-      </c>
-      <c r="D7" t="e">
-        <f>D5-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E7">
-        <f>E5-E7</f>
-        <v>45066</v>
-      </c>
-      <c r="F7">
-        <f>F5-F7</f>
-        <v>45732</v>
-      </c>
-      <c r="G7">
-        <f>G5-G7</f>
-        <v>46398</v>
-      </c>
-      <c r="H7">
-        <f>H5-H7</f>
-        <v>46176</v>
-      </c>
-      <c r="I7">
-        <f>I5-I7</f>
-        <v>46031.3</v>
-      </c>
-      <c r="J7">
-        <f>J5-J7</f>
-        <v>47108.17</v>
-      </c>
-      <c r="K7">
-        <f>K5-K7</f>
-        <v>46953</v>
-      </c>
-      <c r="L7">
-        <f>L5-L7</f>
-        <v>48618</v>
-      </c>
-      <c r="M7">
-        <f>M5-M7</f>
-        <v>53280</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>编制日期</t>
-        </is>
-      </c>
-      <c r="B8">
         <f>TODAY()</f>
         <v>46270</v>
       </c>
@@ -798,6 +732,272 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:N5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>华宸物业 2026 年月度营业收入与上年同期（万元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1月</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2月</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>7月</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>10月</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>12月</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>全年</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>本年营业收入</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>月度收入!B5</f>
+        <v>43845</v>
+      </c>
+      <c r="C3">
+        <f>月度收入!C5</f>
+        <v>41958</v>
+      </c>
+      <c r="D3">
+        <f>月度收入!D5</f>
+        <v>44511</v>
+      </c>
+      <c r="E3">
+        <f>月度收入!E5</f>
+        <v>45066</v>
+      </c>
+      <c r="F3">
+        <f>月度收入!F5</f>
+        <v>45732</v>
+      </c>
+      <c r="G3">
+        <f>月度收入!G5</f>
+        <v>46398</v>
+      </c>
+      <c r="H3">
+        <f>月度收入!H5</f>
+        <v>46176</v>
+      </c>
+      <c r="I3">
+        <f>月度收入!I5</f>
+        <v>46031.3</v>
+      </c>
+      <c r="J3">
+        <f>月度收入!J5</f>
+        <v>47108.17</v>
+      </c>
+      <c r="K3">
+        <f>月度收入!K5</f>
+        <v>46953</v>
+      </c>
+      <c r="L3">
+        <f>月度收入!L5</f>
+        <v>48618</v>
+      </c>
+      <c r="M3">
+        <f>月度收入!M5</f>
+        <v>53280</v>
+      </c>
+      <c r="N3">
+        <f>SUM(B3:M3)</f>
+        <v>555676.47</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>上年同期（外部链接）</t>
+        </is>
+      </c>
+      <c r="B4" t="e">
+        <f>'[2025年报.xlsx]利润表'!B6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C4" t="e">
+        <f>'[2025年报.xlsx]利润表'!C6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D4" t="e">
+        <f>'[2025年报.xlsx]利润表'!D6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E4" t="e">
+        <f>'[2025年报.xlsx]利润表'!E6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F4" t="e">
+        <f>'[2025年报.xlsx]利润表'!F6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="G4" t="e">
+        <f>'[2025年报.xlsx]利润表'!G6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H4" t="e">
+        <f>'[2025年报.xlsx]利润表'!H6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I4" t="e">
+        <f>'[2025年报.xlsx]利润表'!I6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J4" t="e">
+        <f>'[2025年报.xlsx]利润表'!J6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K4" t="e">
+        <f>'[2025年报.xlsx]利润表'!K6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L4" t="e">
+        <f>'[2025年报.xlsx]利润表'!L6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M4" t="e">
+        <f>'[2025年报.xlsx]利润表'!M6</f>
+        <v>#REF!</v>
+      </c>
+      <c r="N4" t="e">
+        <f>SUM(B4:M4)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>同比差额</t>
+        </is>
+      </c>
+      <c r="B5" t="e">
+        <f>B3-B4</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C5" t="e">
+        <f>C3-C4</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D5" t="e">
+        <f>D3-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E5" t="e">
+        <f>E3-E4</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F5" t="e">
+        <f>F3-F4</f>
+        <v>#REF!</v>
+      </c>
+      <c r="G5" t="e">
+        <f>G3-G4</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H5" t="e">
+        <f>H3-H4</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I5" t="e">
+        <f>I3-I4</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J5" t="e">
+        <f>J3-J4</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K5" t="e">
+        <f>K3-K4</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L5" t="e">
+        <f>L3-L4</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M5" t="e">
+        <f>M3-M4</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
